--- a/문서함/PM/PM 일정 문서.xlsx
+++ b/문서함/PM/PM 일정 문서.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="시트3" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="1년 목표" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="26.03.00~00 양식" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="26.03.10~16" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="26.03.17~23" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="26.03.24~30" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="1주차  26.03.10~16" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="2주차  26.03.17~23" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="3주차  26.03.24~30" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="143">
   <si>
     <t>기간</t>
   </si>
@@ -411,32 +411,155 @@
     <t>6일</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>투사-마력폭탄 카드</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>투사 - 그림자 묶기 카드</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>투사 - 견제 사격 카드</t>
+    </r>
+  </si>
+  <si>
+    <t>덱 아키타입 - 벽쿵/격퇴 덱 + 관련 유물 7종</t>
+  </si>
+  <si>
+    <t>26.03.24~26.03.28</t>
+  </si>
+  <si>
+    <t>5일</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/b301809e96cc9aa772c8ed407683ae2b4d7e0a00</t>
+  </si>
+  <si>
+    <t>영역 카드 5장 구현</t>
+  </si>
+  <si>
     <t>진행 중</t>
   </si>
   <si>
-    <t>카드 덱 1개 기획</t>
-  </si>
-  <si>
-    <t>26.03.24~26.03.28</t>
-  </si>
-  <si>
-    <t>5일</t>
-  </si>
-  <si>
-    <t>영역 카드 5장 구현</t>
-  </si>
-  <si>
     <t>카드 기획서 작성</t>
   </si>
   <si>
     <t>26.03.26~26.03.31</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>1차 작성</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>기획서에 작성된 카드 작성</t>
+    </r>
+  </si>
+  <si>
+    <t>카드 기획서 - 신규 카드 작성</t>
+  </si>
+  <si>
+    <t>26.03.27~26.03.31</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/a6a95cb5a0438e0bff6d24a746ac8fe779d753ed</t>
+  </si>
+  <si>
+    <t>벽쿵/격퇴 덱 카드 : 7종 기획</t>
+  </si>
+  <si>
+    <t>26.03.26~26.03.28</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/9fc884f4c7a0125167a613d3ef837221d25a8c18</t>
+  </si>
+  <si>
+    <t>디스코드 웹훅을 이용하여 마감 알림 구축</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>26.03.27~26.03.27</t>
+  </si>
+  <si>
+    <t>1일</t>
+  </si>
+  <si>
+    <t>폭팔 타입 기능 수정 - x자 모양으로 수정</t>
+  </si>
+  <si>
+    <t>26.03.28~26.03.29</t>
+  </si>
+  <si>
+    <t>영역 카드 기획서 수정</t>
+  </si>
+  <si>
+    <t>26.03.28~26.03.30</t>
+  </si>
+  <si>
+    <t>카드 선택 인터랙션 수정</t>
+  </si>
+  <si>
+    <t>기술 카드 파트 부분 카드 제작 (12장 구현) [1, 2, 3, 9, 10, 11, 12, 13, 14, 15, 16, 17]</t>
+  </si>
+  <si>
+    <t>26.03.28~26.03.31</t>
+  </si>
+  <si>
+    <t>손패 선택 방식 기획서 작성</t>
+  </si>
+  <si>
+    <t>26.03.28~26.03.28</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/828ea77b69c8cbacdfd63f02632e3e32fca67634</t>
+  </si>
+  <si>
+    <t>대미지 계산식 관련 기획서 작성</t>
+  </si>
+  <si>
+    <t>26.03.29~26.03.31</t>
+  </si>
+  <si>
+    <t>대기</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -447,6 +570,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -501,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -535,6 +666,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,7 +1097,7 @@
     <col customWidth="1" min="1" max="1" width="91.13"/>
     <col customWidth="1" min="4" max="4" width="20.0"/>
     <col customWidth="1" min="5" max="5" width="7.75"/>
-    <col customWidth="1" min="8" max="8" width="36.75"/>
+    <col customWidth="1" min="8" max="8" width="63.5"/>
     <col customWidth="1" min="9" max="9" width="4.25"/>
     <col customWidth="1" min="11" max="11" width="63.13"/>
   </cols>
@@ -2270,6 +2407,9 @@
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2592,8 +2732,9 @@
     <hyperlink r:id="rId5" ref="H6"/>
     <hyperlink r:id="rId6" ref="H7"/>
     <hyperlink r:id="rId7" ref="H8"/>
+    <hyperlink r:id="rId8" ref="H9"/>
   </hyperlinks>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -2664,9 +2805,11 @@
         <v>67</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>114</v>
+      </c>
       <c r="J2" s="5" t="s">
         <v>39</v>
       </c>
@@ -2676,7 +2819,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>70</v>
@@ -2694,7 +2837,7 @@
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H3" s="4"/>
       <c r="J3" s="6" t="s">
@@ -2706,7 +2849,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>56</v>
@@ -2715,7 +2858,7 @@
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>109</v>
@@ -2724,9 +2867,11 @@
         <v>81</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>119</v>
+      </c>
       <c r="J4" s="7" t="s">
         <v>43</v>
       </c>
@@ -2735,14 +2880,30 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
+        <v>121</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="J5" s="8" t="s">
         <v>45</v>
       </c>
@@ -2751,84 +2912,199 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="A6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9">
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10">
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+        <v>131</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11">
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12">
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
+        <v>138</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14">
@@ -3131,6 +3407,13 @@
       <formula1>"대기,진행 중,테스트 중,완료,추가 연장 진행,보류"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="H2"/>
+    <hyperlink r:id="rId2" ref="H4"/>
+    <hyperlink r:id="rId3" ref="H5"/>
+    <hyperlink r:id="rId4" ref="H6"/>
+    <hyperlink r:id="rId5" ref="H12"/>
+  </hyperlinks>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
--- a/문서함/PM/PM 일정 문서.xlsx
+++ b/문서함/PM/PM 일정 문서.xlsx
@@ -4,10 +4,12 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="1년 목표" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="26.03.00~00 양식" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="N주차  26.03.00~00 양식" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="1주차  26.03.10~16" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="2주차  26.03.17~23" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="3주차  26.03.24~30" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="4주차  26.03.31~04.06" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="5주차  26.04.07~13" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="159">
   <si>
     <t>기간</t>
   </si>
@@ -131,7 +133,7 @@
     <t>설명</t>
   </si>
   <si>
-    <t>26.03.00~26.03.00</t>
+    <t>26.04.00~26.04.00</t>
   </si>
   <si>
     <t>초록색 배경</t>
@@ -149,7 +151,7 @@
     <t>빨간색 배경</t>
   </si>
   <si>
-    <t>오류난 부분 수정</t>
+    <t>오류난 부분 수정, 긴급한 업무</t>
   </si>
   <si>
     <t>보라색 배경</t>
@@ -402,7 +404,7 @@
     <t>https://github.com/Taehyeon88/Graduation-project/commit/e64ed40504703208a24d567d425220d538f04a24</t>
   </si>
   <si>
-    <t>공격 카드 3개 제작</t>
+    <t>공격 카드 3개 제작 (투사 3종) [마력폭탄, 그림자 묶기, 견제 사격]</t>
   </si>
   <si>
     <t>26.03.21~26.03.26</t>
@@ -442,6 +444,9 @@
     </r>
   </si>
   <si>
+    <t>26.03.00~26.03.00</t>
+  </si>
+  <si>
     <t>덱 아키타입 - 벽쿵/격퇴 덱 + 관련 유물 7종</t>
   </si>
   <si>
@@ -457,7 +462,60 @@
     <t>영역 카드 5장 구현</t>
   </si>
   <si>
-    <t>진행 중</t>
+    <t>완료, 지연</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>영역효과 기능 구현 및 불타는 잿빛 영역 효과/카드 구현</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>AoE_오브젝트 계열_횟수기반으로 확장 및 거미줄 함정 AoE/카드 구현</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>영역_기술_성역의 문양 카드 구현</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>기술_영역_맹독의 늪 카드 구현</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>집중 상태효과/회복/기술_영역_빛의 웅덩이 AoE/카드 구현 및 대상/그리드 지정 개념 추가</t>
+    </r>
   </si>
   <si>
     <t>카드 기획서 작성</t>
@@ -486,6 +544,9 @@
     </r>
   </si>
   <si>
+    <t>오류난 부분 수정</t>
+  </si>
+  <si>
     <t>카드 기획서 - 신규 카드 작성</t>
   </si>
   <si>
@@ -522,12 +583,18 @@
     <t>26.03.28~26.03.29</t>
   </si>
   <si>
+    <t>진행 중, 지연</t>
+  </si>
+  <si>
     <t>영역 카드 기획서 수정</t>
   </si>
   <si>
     <t>26.03.28~26.03.30</t>
   </si>
   <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/c52c402cde207dbd0951b071f57c9f6a3481f1ce</t>
+  </si>
+  <si>
     <t>카드 선택 인터랙션 수정</t>
   </si>
   <si>
@@ -537,6 +604,9 @@
     <t>26.03.28~26.03.31</t>
   </si>
   <si>
+    <t>진행 중</t>
+  </si>
+  <si>
     <t>손패 선택 방식 기획서 작성</t>
   </si>
   <si>
@@ -552,7 +622,37 @@
     <t>26.03.29~26.03.31</t>
   </si>
   <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/ca925ce203ada5c6be1696db0238808dfae2b282</t>
+  </si>
+  <si>
+    <t>상태효과 기획서 작성 + 몬스터가 해당 턴에 얻은 효과를 유지하는 방법</t>
+  </si>
+  <si>
+    <t>26.03.31~26.04.02</t>
+  </si>
+  <si>
+    <t>대미지 연산 시스템 연산식 수정</t>
+  </si>
+  <si>
+    <t>26.04.06~26.04.06</t>
+  </si>
+  <si>
     <t>대기</t>
+  </si>
+  <si>
+    <t>빌드 디버깅 + 치트 시스템 기능 구현</t>
+  </si>
+  <si>
+    <t>26.04.02~26.04.02</t>
+  </si>
+  <si>
+    <t>아키타입 : 벽쿵/격퇴 덱 카드 7종 구현</t>
+  </si>
+  <si>
+    <t>26.04.03~26.04.07</t>
+  </si>
+  <si>
+    <t>전투 공격 연출</t>
   </si>
 </sst>
 </file>
@@ -749,6 +849,14 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1097,6 +1205,7 @@
     <col customWidth="1" min="1" max="1" width="91.13"/>
     <col customWidth="1" min="4" max="4" width="20.0"/>
     <col customWidth="1" min="5" max="5" width="7.75"/>
+    <col customWidth="1" min="7" max="7" width="23.38"/>
     <col customWidth="1" min="8" max="8" width="63.5"/>
     <col customWidth="1" min="9" max="9" width="4.25"/>
     <col customWidth="1" min="11" max="11" width="63.13"/>
@@ -1532,7 +1641,7 @@
   </sheetData>
   <conditionalFormatting sqref="A2:H38">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2="완료"</formula>
+      <formula>SEARCH("완료", $G2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:H38">
@@ -1565,6 +1674,16 @@
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A104">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="8">
+      <formula>LEN(TRIM(A104))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A104">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="9">
+      <formula>LEN(TRIM(A104))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F38">
       <formula1>"버그 수정,기능 개발,기능 수정,기획,테스트,코드 수정 및 정리,발표 자료 제작,밸런스 조정,출시 준비,문서 작성"</formula1>
@@ -1572,11 +1691,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C38">
       <formula1>"김덕용,문태현"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G38">
+      <formula1>"대기,진행 중,테스트 중,완료,추가 연장 진행,보류,지연"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B38">
       <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G38">
-      <formula1>"대기,진행 중,테스트 중,완료,추가 연장 진행,보류"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>
@@ -2417,7 +2536,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -2426,7 +2545,7 @@
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -2435,7 +2554,7 @@
       <c r="B12" s="3"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -2444,7 +2563,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -2453,7 +2572,7 @@
       <c r="B14" s="3"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -2462,7 +2581,7 @@
       <c r="B15" s="3"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -2471,7 +2590,7 @@
       <c r="B16" s="3"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -2480,7 +2599,7 @@
       <c r="B17" s="3"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -2489,7 +2608,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2498,7 +2617,7 @@
       <c r="B19" s="3"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -2507,7 +2626,7 @@
       <c r="B20" s="3"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2516,7 +2635,7 @@
       <c r="B21" s="3"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -2525,7 +2644,7 @@
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -2534,7 +2653,7 @@
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -2543,7 +2662,7 @@
       <c r="B24" s="3"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -2552,7 +2671,7 @@
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -2561,7 +2680,7 @@
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -2570,7 +2689,7 @@
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -2579,7 +2698,7 @@
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -2588,7 +2707,7 @@
       <c r="B29" s="3"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -2597,7 +2716,7 @@
       <c r="B30" s="3"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -2606,7 +2725,7 @@
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -2615,7 +2734,7 @@
       <c r="B32" s="3"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -2624,7 +2743,7 @@
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -2633,7 +2752,7 @@
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -2642,7 +2761,7 @@
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -2651,7 +2770,7 @@
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -2660,7 +2779,7 @@
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -2669,7 +2788,7 @@
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -2748,6 +2867,7 @@
     <col customWidth="1" min="1" max="1" width="91.13"/>
     <col customWidth="1" min="4" max="4" width="20.0"/>
     <col customWidth="1" min="5" max="5" width="7.75"/>
+    <col customWidth="1" min="7" max="7" width="20.63"/>
     <col customWidth="1" min="8" max="8" width="37.13"/>
     <col customWidth="1" min="9" max="9" width="4.0"/>
     <col customWidth="1" min="11" max="11" width="38.0"/>
@@ -2787,7 +2907,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>56</v>
@@ -2796,10 +2916,10 @@
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>67</v>
@@ -2808,7 +2928,7 @@
         <v>53</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>39</v>
@@ -2819,7 +2939,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>70</v>
@@ -2828,18 +2948,20 @@
         <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="4"/>
+        <v>117</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="J3" s="6" t="s">
         <v>41</v>
       </c>
@@ -2849,7 +2971,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>56</v>
@@ -2858,7 +2980,7 @@
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>109</v>
@@ -2870,18 +2992,18 @@
         <v>53</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>43</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>56</v>
@@ -2890,10 +3012,10 @@
         <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>81</v>
@@ -2902,7 +3024,7 @@
         <v>53</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>45</v>
@@ -2913,7 +3035,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>56</v>
@@ -2922,7 +3044,7 @@
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>72</v>
@@ -2934,24 +3056,24 @@
         <v>53</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>62</v>
@@ -2963,7 +3085,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>56</v>
@@ -2972,7 +3094,7 @@
         <v>49</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>51</v>
@@ -2981,13 +3103,13 @@
         <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>48</v>
@@ -2996,7 +3118,7 @@
         <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>72</v>
@@ -3005,13 +3127,15 @@
         <v>67</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H9" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>48</v>
@@ -3020,7 +3144,7 @@
         <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>51</v>
@@ -3029,13 +3153,13 @@
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>70</v>
@@ -3044,7 +3168,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>66</v>
@@ -3053,13 +3177,13 @@
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>70</v>
@@ -3068,10 +3192,10 @@
         <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>67</v>
@@ -3080,12 +3204,12 @@
         <v>53</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>56</v>
@@ -3094,7 +3218,7 @@
         <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>72</v>
@@ -3103,15 +3227,17 @@
         <v>67</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H13" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="3"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -3121,17 +3247,17 @@
       <c r="B15" s="3"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16">
       <c r="B16" s="3"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -3141,7 +3267,7 @@
       <c r="B17" s="3"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -3151,7 +3277,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -3161,7 +3287,7 @@
       <c r="B19" s="3"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -3171,7 +3297,7 @@
       <c r="B20" s="3"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -3181,17 +3307,17 @@
       <c r="B21" s="3"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="11"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22">
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -3201,7 +3327,7 @@
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -3211,7 +3337,7 @@
       <c r="B24" s="3"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -3221,7 +3347,7 @@
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -3231,7 +3357,7 @@
       <c r="B26" s="3"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -3241,7 +3367,7 @@
       <c r="B27" s="3"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -3251,7 +3377,7 @@
       <c r="B28" s="3"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -3261,7 +3387,7 @@
       <c r="B29" s="3"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -3271,7 +3397,7 @@
       <c r="B30" s="3"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -3281,7 +3407,7 @@
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -3291,7 +3417,7 @@
       <c r="B32" s="3"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -3301,7 +3427,7 @@
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -3311,7 +3437,7 @@
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -3321,7 +3447,7 @@
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -3331,7 +3457,7 @@
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -3341,7 +3467,7 @@
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -3351,7 +3477,7 @@
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="2" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -3360,7 +3486,7 @@
   </sheetData>
   <conditionalFormatting sqref="A2:H38">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2="완료"</formula>
+      <formula>SEARCH("완료", $G2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:H38">
@@ -3400,20 +3526,1092 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C38">
       <formula1>"김덕용,문태현"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G38">
+      <formula1>"대기,진행 중,테스트 중,완료,추가 연장 진행,보류,지연"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B38">
       <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G38">
-      <formula1>"대기,진행 중,테스트 중,완료,추가 연장 진행,보류"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="H2"/>
-    <hyperlink r:id="rId2" ref="H4"/>
-    <hyperlink r:id="rId3" ref="H5"/>
-    <hyperlink r:id="rId4" ref="H6"/>
-    <hyperlink r:id="rId5" ref="H12"/>
+    <hyperlink r:id="rId2" ref="H3"/>
+    <hyperlink r:id="rId3" ref="H4"/>
+    <hyperlink r:id="rId4" ref="H5"/>
+    <hyperlink r:id="rId5" ref="H6"/>
+    <hyperlink r:id="rId6" ref="H9"/>
+    <hyperlink r:id="rId7" ref="H12"/>
+    <hyperlink r:id="rId8" ref="H13"/>
   </hyperlinks>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="91.13"/>
+    <col customWidth="1" min="4" max="4" width="20.0"/>
+    <col customWidth="1" min="5" max="5" width="7.75"/>
+    <col customWidth="1" min="7" max="7" width="23.38"/>
+    <col customWidth="1" min="8" max="8" width="63.5"/>
+    <col customWidth="1" min="9" max="9" width="4.25"/>
+    <col customWidth="1" min="11" max="11" width="63.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="J2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="J3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="J4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="J5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="3"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="3"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="3"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="3"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="3"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="3"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="3"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="3"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>SEARCH("완료", $G2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$G2="보류"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$F2="버그 수정"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>AND(RIGHT($D2, 2)&lt;&gt;"00", TODAY() &gt; DATE(2000+LEFT(RIGHT($D2, 8), 2), MID(RIGHT($D2, 8), 4, 2), RIGHT($D2, 2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(F42))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="6">
+      <formula>LEN(TRIM(H16))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="7">
+      <formula>LEN(TRIM(H16))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F38">
+      <formula1>"버그 수정,기능 개발,기능 수정,기획,테스트,코드 수정 및 정리,발표 자료 제작,밸런스 조정,출시 준비,문서 작성"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G38">
+      <formula1>"대기,진행 중,테스트 중,완료,추가 연장 진행,보류,지각"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C38">
+      <formula1>"김덕용,문태현"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B38">
+      <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="91.13"/>
+    <col customWidth="1" min="4" max="4" width="20.0"/>
+    <col customWidth="1" min="5" max="5" width="7.75"/>
+    <col customWidth="1" min="7" max="7" width="23.38"/>
+    <col customWidth="1" min="8" max="8" width="63.5"/>
+    <col customWidth="1" min="9" max="9" width="4.25"/>
+    <col customWidth="1" min="11" max="11" width="63.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="4"/>
+      <c r="J2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="4"/>
+      <c r="J3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="J4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="J5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="3"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="3"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="3"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="3"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="3"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="3"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="3"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="3"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="3"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="3"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="4"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>SEARCH("완료", $G2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$G2="보류"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$F2="버그 수정"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H38">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>AND(RIGHT($D2, 2)&lt;&gt;"00", TODAY() &gt; DATE(2000+LEFT(RIGHT($D2, 8), 2), MID(RIGHT($D2, 8), 4, 2), RIGHT($D2, 2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(F42))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="6">
+      <formula>LEN(TRIM(H16))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="7">
+      <formula>LEN(TRIM(H16))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A104">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="8">
+      <formula>LEN(TRIM(A104))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A104">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="9">
+      <formula>LEN(TRIM(A104))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F38">
+      <formula1>"버그 수정,기능 개발,기능 수정,기획,테스트,코드 수정 및 정리,발표 자료 제작,밸런스 조정,출시 준비,문서 작성"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G38">
+      <formula1>"대기,진행 중,테스트 중,완료,추가 연장 진행,보류,지각"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C38">
+      <formula1>"김덕용,문태현"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B38">
+      <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/문서함/PM/PM 일정 문서.xlsx
+++ b/문서함/PM/PM 일정 문서.xlsx
@@ -4,12 +4,13 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="1년 목표" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="N주차  26.03.00~00 양식" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="1주차  26.03.10~16" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="2주차  26.03.17~23" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="3주차  26.03.24~30" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="4주차  26.03.31~04.06" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="5주차  26.04.07~13" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="추후 할일" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="N주차  26.03.00~00 양식" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="1주차  26.03.10~16" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="2주차  26.03.17~23" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="3주차  26.03.24~30" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="4주차  26.03.31~04.06" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="5주차  26.04.07~13" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="179">
   <si>
     <t>기간</t>
   </si>
@@ -106,6 +107,42 @@
     <t>?/? - 8주</t>
   </si>
   <si>
+    <t>담당자</t>
+  </si>
+  <si>
+    <t>할일</t>
+  </si>
+  <si>
+    <t>계열</t>
+  </si>
+  <si>
+    <t>문태현</t>
+  </si>
+  <si>
+    <t>전투 공격 연출</t>
+  </si>
+  <si>
+    <t>기능 개발</t>
+  </si>
+  <si>
+    <t>단축키 기능 추가 [손패 단축키 등]</t>
+  </si>
+  <si>
+    <t>기능 추가</t>
+  </si>
+  <si>
+    <t>김덕용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">키바인딩 기획서 </t>
+  </si>
+  <si>
+    <t>기획</t>
+  </si>
+  <si>
+    <t>아키타입 : 타격기동 덱</t>
+  </si>
+  <si>
     <t>할 일</t>
   </si>
   <si>
@@ -166,9 +203,6 @@
     <t>P0</t>
   </si>
   <si>
-    <t>문태현</t>
-  </si>
-  <si>
     <t>26.03.10~26.00.12</t>
   </si>
   <si>
@@ -205,22 +239,13 @@
     <t>26.03.10~26.03.12</t>
   </si>
   <si>
-    <t>기능 개발</t>
-  </si>
-  <si>
     <t>버프/디버프 카드 기획 작성</t>
   </si>
   <si>
-    <t>김덕용</t>
-  </si>
-  <si>
     <t>26.03.10~26.03.14</t>
   </si>
   <si>
     <t>4일</t>
-  </si>
-  <si>
-    <t>기획</t>
   </si>
   <si>
     <t>https://github.com/Taehyeon88/Graduation-project/commit/9d8ada51428dfe7feba978f0e906cc94b159c0b9</t>
@@ -445,6 +470,9 @@
   </si>
   <si>
     <t>26.03.00~26.03.00</t>
+  </si>
+  <si>
+    <t>비고</t>
   </si>
   <si>
     <t>덱 아키타입 - 벽쿵/격퇴 덱 + 관련 유물 7종</t>
@@ -583,7 +611,10 @@
     <t>26.03.28~26.03.29</t>
   </si>
   <si>
-    <t>진행 중, 지연</t>
+    <t>지연, 완료</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/beb24f5fc840075d01405fdc59dbb0da52314c36</t>
   </si>
   <si>
     <t>영역 카드 기획서 수정</t>
@@ -598,61 +629,108 @@
     <t>카드 선택 인터랙션 수정</t>
   </si>
   <si>
+    <t>단축키 제외 완성, 추후 R&amp;D 이후 모든 단축키 제작할 예정</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>신_손패 연출 시스템 구조 구현</t>
+    </r>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>카드 시스템_카드 타겟모드_자가 적용형 기능 업데이트 및 커스텀 RM, TM 기능 확장</t>
+    </r>
+  </si>
+  <si>
     <t>기술 카드 파트 부분 카드 제작 (12장 구현) [1, 2, 3, 9, 10, 11, 12, 13, 14, 15, 16, 17]</t>
   </si>
   <si>
-    <t>26.03.28~26.03.31</t>
+    <t>26.03.28~26.04.03</t>
+  </si>
+  <si>
+    <t>7일</t>
+  </si>
+  <si>
+    <t>지연, 추가 연장 진행</t>
+  </si>
+  <si>
+    <t>마감일 31일 지연</t>
+  </si>
+  <si>
+    <t>손패 선택 방식 기획서 작성</t>
+  </si>
+  <si>
+    <t>26.03.28~26.03.28</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/828ea77b69c8cbacdfd63f02632e3e32fca67634</t>
+  </si>
+  <si>
+    <t>대미지 계산식 관련 기획서 작성</t>
+  </si>
+  <si>
+    <t>26.03.29~26.03.31</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/ca925ce203ada5c6be1696db0238808dfae2b282</t>
+  </si>
+  <si>
+    <t>상태효과 기획서 작성 + 몬스터가 해당 턴에 얻은 효과를 유지하는 방법</t>
+  </si>
+  <si>
+    <t>26.03.31~26.04.02</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/4dd031a78180f98ba228bd1611c639dd331f8d6a</t>
+  </si>
+  <si>
+    <t>대미지 연산 시스템 연산식 수정</t>
+  </si>
+  <si>
+    <t>26.04.06~26.04.06</t>
+  </si>
+  <si>
+    <t>https://github.com/Taehyeon88/Graduation-project/commit/6848cb1bb2a20aaf6a2e27791d5e0d915327f368</t>
+  </si>
+  <si>
+    <t>빌드 디버깅 + 치트 시스템 기능 구현</t>
+  </si>
+  <si>
+    <t>26.04.02~26.04.02</t>
   </si>
   <si>
     <t>진행 중</t>
   </si>
   <si>
-    <t>손패 선택 방식 기획서 작성</t>
-  </si>
-  <si>
-    <t>26.03.28~26.03.28</t>
-  </si>
-  <si>
-    <t>https://github.com/Taehyeon88/Graduation-project/commit/828ea77b69c8cbacdfd63f02632e3e32fca67634</t>
-  </si>
-  <si>
-    <t>대미지 계산식 관련 기획서 작성</t>
-  </si>
-  <si>
-    <t>26.03.29~26.03.31</t>
-  </si>
-  <si>
-    <t>https://github.com/Taehyeon88/Graduation-project/commit/ca925ce203ada5c6be1696db0238808dfae2b282</t>
-  </si>
-  <si>
-    <t>상태효과 기획서 작성 + 몬스터가 해당 턴에 얻은 효과를 유지하는 방법</t>
-  </si>
-  <si>
-    <t>26.03.31~26.04.02</t>
-  </si>
-  <si>
-    <t>대미지 연산 시스템 연산식 수정</t>
-  </si>
-  <si>
-    <t>26.04.06~26.04.06</t>
+    <t>아키타입 : 벽쿵/격퇴 덱 카드 7종 구현</t>
+  </si>
+  <si>
+    <t>26.04.03~26.04.07</t>
   </si>
   <si>
     <t>대기</t>
   </si>
   <si>
-    <t>빌드 디버깅 + 치트 시스템 기능 구현</t>
-  </si>
-  <si>
-    <t>26.04.02~26.04.02</t>
-  </si>
-  <si>
-    <t>아키타입 : 벽쿵/격퇴 덱 카드 7종 구현</t>
-  </si>
-  <si>
-    <t>26.04.03~26.04.07</t>
-  </si>
-  <si>
-    <t>전투 공격 연출</t>
+    <t>손패 연출 기획서 연출 일부 변경</t>
+  </si>
+  <si>
+    <t>26.04.02~26.04.03</t>
+  </si>
+  <si>
+    <t>카드 더미 기획서 + UI창 일부 제작</t>
+  </si>
+  <si>
+    <t>26.04.03~26.04.04</t>
   </si>
 </sst>
 </file>
@@ -732,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -741,6 +819,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -767,7 +848,13 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -857,6 +944,10 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1202,13 +1293,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="91.13"/>
-    <col customWidth="1" min="4" max="4" width="20.0"/>
-    <col customWidth="1" min="5" max="5" width="7.75"/>
-    <col customWidth="1" min="7" max="7" width="23.38"/>
-    <col customWidth="1" min="8" max="8" width="63.5"/>
-    <col customWidth="1" min="9" max="9" width="4.25"/>
-    <col customWidth="1" min="11" max="11" width="63.13"/>
+    <col customWidth="1" min="1" max="1" width="13.88"/>
+    <col customWidth="1" min="2" max="2" width="113.75"/>
+    <col customWidth="1" min="3" max="3" width="16.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1221,440 +1308,548 @@
       <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="91.13"/>
+    <col customWidth="1" min="4" max="4" width="20.0"/>
+    <col customWidth="1" min="5" max="5" width="7.75"/>
+    <col customWidth="1" min="7" max="7" width="23.38"/>
+    <col customWidth="1" min="8" max="9" width="63.5"/>
+    <col customWidth="1" min="10" max="10" width="4.25"/>
+    <col customWidth="1" min="12" max="12" width="63.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="4"/>
-      <c r="J2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="K2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="4"/>
-      <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>42</v>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="K3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="J4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>44</v>
+      <c r="G4" s="4"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="K4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="J5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="K5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9">
-      <c r="B9" s="3"/>
+      <c r="B9" s="4"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10">
-      <c r="B10" s="3"/>
+      <c r="B10" s="4"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11">
-      <c r="B11" s="3"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12">
-      <c r="B12" s="3"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13">
-      <c r="B13" s="3"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14">
-      <c r="B14" s="3"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15">
-      <c r="B15" s="3"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17">
-      <c r="B17" s="3"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18">
-      <c r="B18" s="3"/>
+      <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19">
-      <c r="B19" s="3"/>
+      <c r="B19" s="4"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20">
-      <c r="B20" s="3"/>
+      <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21">
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22">
-      <c r="B22" s="3"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24">
-      <c r="B24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25">
-      <c r="B25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26">
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27">
-      <c r="B27" s="3"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28">
-      <c r="B28" s="3"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29">
-      <c r="B29" s="3"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30">
-      <c r="B30" s="3"/>
+      <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32">
-      <c r="B32" s="3"/>
+      <c r="B32" s="4"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
     </row>
     <row r="35">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
     </row>
     <row r="36">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
     </row>
     <row r="37">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
     </row>
     <row r="38">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>SEARCH("완료", $G2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$G2="보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$F2="버그 수정"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>AND(RIGHT($D2, 2)&lt;&gt;"00", TODAY() &gt; DATE(2000+LEFT(RIGHT($D2, 8), 2), MID(RIGHT($D2, 8), 4, 2), RIGHT($D2, 2)))</formula>
     </cfRule>
@@ -1664,12 +1859,12 @@
       <formula>LEN(TRIM(F42))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H16:I16">
     <cfRule type="notContainsBlanks" dxfId="0" priority="6">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H16:I16">
     <cfRule type="notContainsBlanks" dxfId="0" priority="7">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
@@ -1702,7 +1897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1718,521 +1913,521 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>54</v>
+        <v>64</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>57</v>
+        <v>64</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="H4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>54</v>
+        <v>64</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>68</v>
+      <c r="H6" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>73</v>
+        <v>64</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>75</v>
+        <v>64</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>78</v>
+      <c r="H9" s="11" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>82</v>
+      <c r="H10" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>85</v>
+      <c r="H11" s="10" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13">
-      <c r="B13" s="3"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14">
-      <c r="B14" s="3"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15">
-      <c r="B15" s="3"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17">
-      <c r="B17" s="3"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18">
-      <c r="B18" s="3"/>
+      <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19">
-      <c r="B19" s="3"/>
+      <c r="B19" s="4"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20">
-      <c r="B20" s="3"/>
+      <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21">
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22">
-      <c r="B22" s="3"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24">
-      <c r="B24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25">
-      <c r="B25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26">
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27">
-      <c r="B27" s="3"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28">
-      <c r="B28" s="3"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29">
-      <c r="B29" s="3"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30">
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31">
-      <c r="B31" s="3"/>
+      <c r="B31" s="4"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
       <c r="D32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:H37">
@@ -2284,7 +2479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2300,498 +2495,498 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>90</v>
+      <c r="H2" s="10" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>93</v>
+        <v>64</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>95</v>
+        <v>64</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>98</v>
+        <v>64</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>101</v>
+      <c r="H6" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>103</v>
+        <v>64</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>106</v>
+      <c r="H8" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>110</v>
+        <v>64</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3"/>
+      <c r="B10" s="4"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11">
-      <c r="B11" s="3"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12">
-      <c r="B12" s="3"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13">
-      <c r="B13" s="3"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14">
-      <c r="B14" s="3"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15">
-      <c r="B15" s="3"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17">
-      <c r="B17" s="3"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18">
-      <c r="B18" s="3"/>
+      <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19">
-      <c r="B19" s="3"/>
+      <c r="B19" s="4"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20">
-      <c r="B20" s="3"/>
+      <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21">
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22">
-      <c r="B22" s="3"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24">
-      <c r="B24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25">
-      <c r="B25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26">
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27">
-      <c r="B27" s="3"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28">
-      <c r="B28" s="3"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29">
-      <c r="B29" s="3"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30">
-      <c r="B30" s="3"/>
+      <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32">
-      <c r="B32" s="3"/>
+      <c r="B32" s="4"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:H38">
@@ -2857,7 +3052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2868,638 +3063,687 @@
     <col customWidth="1" min="4" max="4" width="20.0"/>
     <col customWidth="1" min="5" max="5" width="7.75"/>
     <col customWidth="1" min="7" max="7" width="20.63"/>
-    <col customWidth="1" min="8" max="8" width="37.13"/>
-    <col customWidth="1" min="9" max="9" width="4.0"/>
-    <col customWidth="1" min="11" max="11" width="38.0"/>
+    <col customWidth="1" min="8" max="8" width="26.0"/>
+    <col customWidth="1" min="9" max="9" width="37.13"/>
+    <col customWidth="1" min="10" max="10" width="4.0"/>
+    <col customWidth="1" min="12" max="12" width="38.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>36</v>
+        <v>120</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
+      <c r="H2" s="13"/>
+      <c r="I2" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>42</v>
+        <v>126</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>122</v>
+      <c r="H4" s="15"/>
+      <c r="I4" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>46</v>
+      <c r="H5" s="15"/>
+      <c r="I5" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>128</v>
+      <c r="H6" s="13"/>
+      <c r="I6" s="14" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H8" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>138</v>
+      <c r="H9" s="15"/>
+      <c r="I9" s="16" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H10" s="4"/>
+        <v>144</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H11" s="4"/>
+        <v>155</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" s="5"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>145</v>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>148</v>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15">
-      <c r="B15" s="3"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17">
-      <c r="B17" s="3"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18">
-      <c r="B18" s="3"/>
+      <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19">
-      <c r="B19" s="3"/>
+      <c r="B19" s="4"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20">
-      <c r="B20" s="3"/>
+      <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21">
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22">
-      <c r="B22" s="3"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24">
-      <c r="B24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25">
-      <c r="B25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26">
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27">
-      <c r="B27" s="3"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28">
-      <c r="B28" s="3"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29">
-      <c r="B29" s="3"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30">
-      <c r="B30" s="3"/>
+      <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32">
-      <c r="B32" s="3"/>
+      <c r="B32" s="4"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
     </row>
     <row r="35">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
     </row>
     <row r="36">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
     </row>
     <row r="37">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
     </row>
     <row r="38">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>SEARCH("완료", $G2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$G2="보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$F2="버그 수정"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>AND(RIGHT($D2, 2)&lt;&gt;"00", TODAY() &gt; DATE(2000+LEFT(RIGHT($D2, 8), 2), MID(RIGHT($D2, 8), 4, 2), RIGHT($D2, 2)))</formula>
     </cfRule>
@@ -3509,12 +3753,12 @@
       <formula>LEN(TRIM(F42))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H16:I16">
     <cfRule type="notContainsBlanks" dxfId="0" priority="6">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H16:I16">
     <cfRule type="notContainsBlanks" dxfId="0" priority="7">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
@@ -3534,535 +3778,610 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="H2"/>
-    <hyperlink r:id="rId2" ref="H3"/>
-    <hyperlink r:id="rId3" ref="H4"/>
-    <hyperlink r:id="rId4" ref="H5"/>
-    <hyperlink r:id="rId5" ref="H6"/>
-    <hyperlink r:id="rId6" ref="H9"/>
-    <hyperlink r:id="rId7" ref="H12"/>
-    <hyperlink r:id="rId8" ref="H13"/>
+    <hyperlink r:id="rId1" ref="I2"/>
+    <hyperlink r:id="rId2" ref="I3"/>
+    <hyperlink r:id="rId3" ref="I4"/>
+    <hyperlink r:id="rId4" ref="I5"/>
+    <hyperlink r:id="rId5" ref="I6"/>
+    <hyperlink r:id="rId6" ref="I8"/>
+    <hyperlink r:id="rId7" ref="I9"/>
+    <hyperlink r:id="rId8" ref="I10"/>
+    <hyperlink r:id="rId9" ref="I12"/>
+    <hyperlink r:id="rId10" ref="I13"/>
   </hyperlinks>
-  <drawing r:id="rId9"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="91.13"/>
+    <col customWidth="1" min="1" max="1" width="79.63"/>
     <col customWidth="1" min="4" max="4" width="20.0"/>
     <col customWidth="1" min="5" max="5" width="7.75"/>
     <col customWidth="1" min="7" max="7" width="23.38"/>
-    <col customWidth="1" min="8" max="8" width="63.5"/>
-    <col customWidth="1" min="9" max="9" width="4.25"/>
-    <col customWidth="1" min="11" max="11" width="63.13"/>
+    <col customWidth="1" min="8" max="8" width="34.5"/>
+    <col customWidth="1" min="9" max="9" width="63.5"/>
+    <col customWidth="1" min="10" max="10" width="4.25"/>
+    <col customWidth="1" min="12" max="12" width="63.13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>36</v>
+        <v>120</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="J2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
+      <c r="H2" s="15"/>
+      <c r="I2" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="J4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>122</v>
+        <v>34</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="K4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="K5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="J5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
+        <v>178</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9">
-      <c r="B9" s="3"/>
+      <c r="B9" s="4"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10">
-      <c r="B10" s="3"/>
+      <c r="B10" s="4"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11">
-      <c r="B11" s="3"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12">
-      <c r="B12" s="3"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13">
-      <c r="B13" s="3"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14">
-      <c r="B14" s="3"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15">
-      <c r="B15" s="3"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17">
-      <c r="B17" s="3"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18">
-      <c r="B18" s="3"/>
+      <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19">
-      <c r="B19" s="3"/>
+      <c r="B19" s="4"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20">
-      <c r="B20" s="3"/>
+      <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21">
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22">
-      <c r="B22" s="3"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24">
-      <c r="B24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25">
-      <c r="B25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
     <row r="26">
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
     </row>
     <row r="27">
-      <c r="B27" s="3"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
     </row>
     <row r="28">
-      <c r="B28" s="3"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
     </row>
     <row r="29">
-      <c r="B29" s="3"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30">
-      <c r="B30" s="3"/>
+      <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32">
-      <c r="B32" s="3"/>
+      <c r="B32" s="4"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
     </row>
     <row r="35">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
     </row>
     <row r="36">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
     </row>
     <row r="37">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
     </row>
     <row r="38">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
+        <v>119</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>SEARCH("완료", $G2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$G2="보류"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$F2="버그 수정"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:H38">
+  <conditionalFormatting sqref="A2:I38">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>AND(RIGHT($D2, 2)&lt;&gt;"00", TODAY() &gt; DATE(2000+LEFT(RIGHT($D2, 8), 2), MID(RIGHT($D2, 8), 4, 2), RIGHT($D2, 2)))</formula>
     </cfRule>
@@ -4072,12 +4391,12 @@
       <formula>LEN(TRIM(F42))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H16:I16">
     <cfRule type="notContainsBlanks" dxfId="0" priority="6">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
+  <conditionalFormatting sqref="H16:I16">
     <cfRule type="notContainsBlanks" dxfId="0" priority="7">
       <formula>LEN(TRIM(H16))&gt;0</formula>
     </cfRule>
@@ -4096,11 +4415,15 @@
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="I2"/>
+    <hyperlink r:id="rId2" ref="I3"/>
+  </hyperlinks>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4118,439 +4441,439 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="5"/>
+      <c r="J2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="5"/>
+      <c r="J3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="5"/>
+      <c r="J4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="4"/>
-      <c r="J2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="4"/>
-      <c r="J3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-      <c r="J4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-      <c r="J5" s="8" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="J5" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9">
-      <c r="B9" s="3"/>
+      <c r="B9" s="4"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10">
-      <c r="B10" s="3"/>
+      <c r="B10" s="4"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11">
-      <c r="B11" s="3"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12">
-      <c r="B12" s="3"/>
+      <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13">
-      <c r="B13" s="3"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14">
-      <c r="B14" s="3"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15">
-      <c r="B15" s="3"/>
+      <c r="B15" s="4"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16">
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17">
-      <c r="B17" s="3"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18">
-      <c r="B18" s="3"/>
+      <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19">
-      <c r="B19" s="3"/>
+      <c r="B19" s="4"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20">
-      <c r="B20" s="3"/>
+      <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21">
-      <c r="B21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22">
-      <c r="B22" s="3"/>
+      <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23">
-      <c r="B23" s="3"/>
+      <c r="B23" s="4"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24">
-      <c r="B24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25">
-      <c r="B25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26">
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27">
-      <c r="B27" s="3"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28">
-      <c r="B28" s="3"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29">
-      <c r="B29" s="3"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30">
-      <c r="B30" s="3"/>
+      <c r="B30" s="4"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32">
-      <c r="B32" s="3"/>
+      <c r="B32" s="4"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33">
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
     </row>
     <row r="34">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
     </row>
     <row r="35">
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
     </row>
     <row r="36">
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
     </row>
     <row r="37">
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
     </row>
     <row r="38">
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:H38">
